--- a/Bosch.xlsx
+++ b/Bosch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\Bosch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAEE0BF-87B3-4C32-8E5C-06F8351A372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB718FE7-AFB9-4933-ACF8-8F72BADC0F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>配方名</t>
   </si>
@@ -92,9 +92,6 @@
     <t>B17</t>
   </si>
   <si>
-    <t>B10</t>
-  </si>
-  <si>
     <t>瓶型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,9 +108,6 @@
     <t>B20</t>
   </si>
   <si>
-    <t>B29</t>
-  </si>
-  <si>
     <t>B19</t>
   </si>
   <si>
@@ -123,9 +117,6 @@
     <t>B21</t>
   </si>
   <si>
-    <t>B23</t>
-  </si>
-  <si>
     <t>B30</t>
   </si>
   <si>
@@ -192,12 +183,6 @@
     <t>B39</t>
   </si>
   <si>
-    <t>B40</t>
-  </si>
-  <si>
-    <t>瓶型</t>
-  </si>
-  <si>
     <t>B42</t>
   </si>
   <si>
@@ -238,6 +223,12 @@
   </si>
   <si>
     <t>B61</t>
+  </si>
+  <si>
+    <t>B70</t>
+  </si>
+  <si>
+    <t>B73</t>
   </si>
 </sst>
 </file>
@@ -279,18 +270,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -305,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -319,13 +304,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -606,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="16" width="20.08203125" bestFit="1" customWidth="1"/>
@@ -618,25 +596,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>1</v>
@@ -671,7 +649,9 @@
       <c r="S1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -731,7 +711,9 @@
       <c r="S2" s="1">
         <v>69.67</v>
       </c>
-      <c r="T2" s="1"/>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -791,7 +773,9 @@
       <c r="S3" s="1">
         <v>51.3</v>
       </c>
-      <c r="T3" s="1"/>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -851,7 +835,9 @@
       <c r="S4" s="1">
         <v>61.46</v>
       </c>
-      <c r="T4" s="1"/>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -911,7 +897,9 @@
       <c r="S5" s="1">
         <v>53.06</v>
       </c>
-      <c r="T5" s="1"/>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -971,7 +959,9 @@
       <c r="S6" s="1">
         <v>51.38</v>
       </c>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1031,14 +1021,16 @@
       <c r="S7" s="2">
         <v>83.45</v>
       </c>
-      <c r="T7" s="1"/>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="B8" s="3">
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>2500</v>
@@ -1049,34 +1041,50 @@
       <c r="E8" s="1">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
-        <v>100</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="1">
+        <v>350</v>
+      </c>
+      <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>1.2</v>
       </c>
       <c r="I8" s="1">
-        <v>432.9</v>
+        <v>413.2</v>
       </c>
       <c r="J8" s="1">
-        <v>2395</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
+        <v>1525</v>
+      </c>
+      <c r="K8" s="1">
+        <v>352.4</v>
+      </c>
+      <c r="L8" s="1">
+        <v>173.2</v>
+      </c>
+      <c r="M8" s="1">
+        <v>42.53</v>
+      </c>
+      <c r="N8" s="1">
+        <v>337.2</v>
+      </c>
+      <c r="O8" s="1">
+        <v>176.2</v>
+      </c>
+      <c r="P8" s="1">
+        <v>39.49</v>
+      </c>
       <c r="Q8" s="1">
-        <v>750.7</v>
-      </c>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="2" t="s">
-        <v>19</v>
+        <v>270.39999999999998</v>
+      </c>
+      <c r="R8" s="1">
+        <v>197.5</v>
+      </c>
+      <c r="S8" s="1">
+        <v>54.68</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -1084,7 +1092,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1">
         <v>2500</v>
@@ -1098,53 +1106,55 @@
       <c r="F9" s="1">
         <v>350</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="1">
         <v>1.2</v>
       </c>
-      <c r="I9" s="1">
-        <v>413.2</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1525</v>
-      </c>
-      <c r="K9" s="1">
-        <v>352.4</v>
-      </c>
-      <c r="L9" s="1">
-        <v>173.2</v>
+      <c r="I9" s="2">
+        <v>395</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1997</v>
+      </c>
+      <c r="K9" s="2">
+        <v>434.5</v>
+      </c>
+      <c r="L9" s="2">
+        <v>228.2</v>
       </c>
       <c r="M9" s="1">
-        <v>42.53</v>
+        <v>43.89</v>
       </c>
       <c r="N9" s="1">
-        <v>337.2</v>
+        <v>395</v>
       </c>
       <c r="O9" s="1">
-        <v>176.2</v>
+        <v>215.1</v>
       </c>
       <c r="P9" s="1">
-        <v>39.49</v>
+        <v>43.89</v>
       </c>
       <c r="Q9" s="1">
-        <v>270.39999999999998</v>
+        <v>324.8</v>
       </c>
       <c r="R9" s="1">
-        <v>197.5</v>
+        <v>289.7</v>
       </c>
       <c r="S9" s="1">
-        <v>54.68</v>
-      </c>
-      <c r="T9" s="1"/>
+        <v>43.89</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3">
-        <v>35</v>
+      <c r="B10" s="1">
+        <v>25</v>
       </c>
       <c r="C10" s="1">
         <v>2500</v>
@@ -1152,48 +1162,54 @@
       <c r="D10" s="1">
         <v>25</v>
       </c>
-      <c r="E10" s="1">
-        <v>300</v>
+      <c r="E10" s="3">
+        <v>700</v>
       </c>
       <c r="F10" s="1">
         <v>350</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="1">
         <v>2</v>
       </c>
       <c r="H10" s="1">
         <v>1.2</v>
       </c>
-      <c r="I10" s="2">
-        <v>395</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1997</v>
-      </c>
-      <c r="K10" s="2">
-        <v>434.5</v>
-      </c>
-      <c r="L10" s="2">
-        <v>228.2</v>
-      </c>
-      <c r="M10" s="1"/>
+      <c r="I10" s="1">
+        <v>393.1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K10" s="1">
+        <v>410.4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>229</v>
+      </c>
+      <c r="M10" s="1">
+        <v>82.08</v>
+      </c>
       <c r="N10" s="1">
-        <v>395</v>
+        <v>388.8</v>
       </c>
       <c r="O10" s="1">
-        <v>215.1</v>
-      </c>
-      <c r="P10" s="1"/>
+        <v>207.4</v>
+      </c>
+      <c r="P10" s="1">
+        <v>73.44</v>
+      </c>
       <c r="Q10" s="1">
-        <v>324.8</v>
+        <v>354.2</v>
       </c>
       <c r="R10" s="1">
-        <v>289.7</v>
+        <v>237.6</v>
       </c>
       <c r="S10" s="1">
-        <v>43.89</v>
-      </c>
-      <c r="T10" s="1"/>
+        <v>51.84</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1202,58 +1218,60 @@
       <c r="B11" s="1">
         <v>25</v>
       </c>
-      <c r="C11" s="1">
-        <v>2500</v>
+      <c r="C11" s="3">
+        <v>3500</v>
       </c>
       <c r="D11" s="1">
         <v>25</v>
       </c>
-      <c r="E11" s="3">
-        <v>700</v>
+      <c r="E11" s="1">
+        <v>300</v>
       </c>
       <c r="F11" s="1">
         <v>350</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="3">
         <v>2</v>
       </c>
       <c r="H11" s="1">
         <v>1.2</v>
       </c>
       <c r="I11" s="1">
-        <v>393.1</v>
+        <v>384.3</v>
       </c>
       <c r="J11" s="1">
-        <v>2022</v>
+        <v>1827</v>
       </c>
       <c r="K11" s="1">
-        <v>410.4</v>
+        <v>347.7</v>
       </c>
       <c r="L11" s="1">
-        <v>229</v>
+        <v>228.8</v>
       </c>
       <c r="M11" s="1">
-        <v>82.08</v>
+        <v>70.16</v>
       </c>
       <c r="N11" s="1">
-        <v>388.8</v>
+        <v>329.4</v>
       </c>
       <c r="O11" s="1">
-        <v>207.4</v>
+        <v>192.2</v>
       </c>
       <c r="P11" s="1">
-        <v>73.44</v>
+        <v>51.86</v>
       </c>
       <c r="Q11" s="1">
-        <v>354.2</v>
+        <v>311.10000000000002</v>
       </c>
       <c r="R11" s="1">
-        <v>237.6</v>
+        <v>210.5</v>
       </c>
       <c r="S11" s="1">
-        <v>51.84</v>
-      </c>
-      <c r="T11" s="1"/>
+        <v>45.76</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1263,7 +1281,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="3">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="D12" s="1">
         <v>25</v>
@@ -1281,39 +1299,41 @@
         <v>1.2</v>
       </c>
       <c r="I12" s="1">
-        <v>384.3</v>
+        <v>363.5</v>
       </c>
       <c r="J12" s="1">
-        <v>1827</v>
+        <v>1731</v>
       </c>
       <c r="K12" s="1">
-        <v>347.7</v>
+        <v>385.8</v>
       </c>
       <c r="L12" s="1">
-        <v>228.8</v>
+        <v>172.2</v>
       </c>
       <c r="M12" s="1">
-        <v>70.16</v>
+        <v>47.83</v>
       </c>
       <c r="N12" s="1">
-        <v>329.4</v>
+        <v>366.7</v>
       </c>
       <c r="O12" s="1">
-        <v>192.2</v>
+        <v>181.7</v>
       </c>
       <c r="P12" s="1">
-        <v>51.86</v>
+        <v>63.77</v>
       </c>
       <c r="Q12" s="1">
-        <v>311.10000000000002</v>
+        <v>325.2</v>
       </c>
       <c r="R12" s="1">
-        <v>210.5</v>
+        <v>216.8</v>
       </c>
       <c r="S12" s="1">
-        <v>45.76</v>
-      </c>
-      <c r="T12" s="1"/>
+        <v>54.2</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1322,11 +1342,11 @@
       <c r="B13" s="1">
         <v>25</v>
       </c>
-      <c r="C13" s="1">
-        <v>2500</v>
-      </c>
-      <c r="D13" s="3">
-        <v>360</v>
+      <c r="C13" s="3">
+        <v>500</v>
+      </c>
+      <c r="D13" s="1">
+        <v>25</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
@@ -1341,38 +1361,40 @@
         <v>1.2</v>
       </c>
       <c r="I13" s="1">
-        <v>370</v>
+        <v>359.5</v>
       </c>
       <c r="J13" s="1">
-        <v>2061</v>
+        <v>1096</v>
       </c>
       <c r="K13" s="1">
-        <v>334.7</v>
+        <v>326</v>
       </c>
       <c r="L13" s="1">
-        <v>170.3</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="M13" s="1">
-        <v>26.99</v>
+        <v>53.59</v>
       </c>
       <c r="N13" s="1">
-        <v>340.6</v>
+        <v>310.39999999999998</v>
       </c>
       <c r="O13" s="1">
-        <v>193.8</v>
+        <v>176.4</v>
       </c>
       <c r="P13" s="1">
-        <v>24.92</v>
+        <v>40.19</v>
       </c>
       <c r="Q13" s="1">
-        <v>411.1</v>
+        <v>256.8</v>
       </c>
       <c r="R13" s="1">
-        <v>193.8</v>
-      </c>
-      <c r="S13" s="1"/>
-      <c r="T13" s="2" t="s">
-        <v>19</v>
+        <v>183.1</v>
+      </c>
+      <c r="S13" s="1">
+        <v>42.43</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
@@ -1382,8 +1404,8 @@
       <c r="B14" s="1">
         <v>25</v>
       </c>
-      <c r="C14" s="3">
-        <v>1500</v>
+      <c r="C14" s="1">
+        <v>2500</v>
       </c>
       <c r="D14" s="1">
         <v>25</v>
@@ -1391,8 +1413,8 @@
       <c r="E14" s="1">
         <v>300</v>
       </c>
-      <c r="F14" s="1">
-        <v>350</v>
+      <c r="F14" s="3">
+        <v>500</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -1401,39 +1423,41 @@
         <v>1.2</v>
       </c>
       <c r="I14" s="1">
-        <v>363.5</v>
+        <v>357.3</v>
       </c>
       <c r="J14" s="1">
-        <v>1731</v>
+        <v>1837</v>
       </c>
       <c r="K14" s="1">
-        <v>385.8</v>
+        <v>189.8</v>
       </c>
       <c r="L14" s="1">
-        <v>172.2</v>
+        <v>396.4</v>
       </c>
       <c r="M14" s="1">
-        <v>47.83</v>
+        <v>72.569999999999993</v>
       </c>
       <c r="N14" s="1">
-        <v>366.7</v>
+        <v>368.4</v>
       </c>
       <c r="O14" s="1">
-        <v>181.7</v>
+        <v>189.8</v>
       </c>
       <c r="P14" s="1">
-        <v>63.77</v>
+        <v>83.74</v>
       </c>
       <c r="Q14" s="1">
-        <v>325.2</v>
+        <v>334.9</v>
       </c>
       <c r="R14" s="1">
-        <v>216.8</v>
+        <v>206.6</v>
       </c>
       <c r="S14" s="1">
-        <v>54.2</v>
-      </c>
-      <c r="T14" s="1"/>
+        <v>78.150000000000006</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -1442,58 +1466,60 @@
       <c r="B15" s="1">
         <v>25</v>
       </c>
-      <c r="C15" s="3">
-        <v>500</v>
+      <c r="C15" s="1">
+        <v>2500</v>
       </c>
       <c r="D15" s="1">
         <v>25</v>
       </c>
-      <c r="E15" s="1">
-        <v>300</v>
+      <c r="E15" s="3">
+        <v>400</v>
       </c>
       <c r="F15" s="1">
         <v>350</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="3">
         <v>2</v>
       </c>
       <c r="H15" s="1">
         <v>1.2</v>
       </c>
       <c r="I15" s="1">
-        <v>359.5</v>
+        <v>328.4</v>
       </c>
       <c r="J15" s="1">
-        <v>1096</v>
+        <v>1827</v>
       </c>
       <c r="K15" s="1">
-        <v>326</v>
+        <v>332.6</v>
       </c>
       <c r="L15" s="1">
-        <v>156.30000000000001</v>
+        <v>265.3</v>
       </c>
       <c r="M15" s="1">
-        <v>53.59</v>
+        <v>50.53</v>
       </c>
       <c r="N15" s="1">
-        <v>310.39999999999998</v>
+        <v>341</v>
       </c>
       <c r="O15" s="1">
-        <v>176.4</v>
+        <v>202.1</v>
       </c>
       <c r="P15" s="1">
-        <v>40.19</v>
+        <v>63.16</v>
       </c>
       <c r="Q15" s="1">
-        <v>256.8</v>
+        <v>282.10000000000002</v>
       </c>
       <c r="R15" s="1">
-        <v>183.1</v>
+        <v>240</v>
       </c>
       <c r="S15" s="1">
-        <v>42.43</v>
-      </c>
-      <c r="T15" s="1"/>
+        <v>37.89</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -1505,55 +1531,57 @@
       <c r="C16" s="1">
         <v>2500</v>
       </c>
-      <c r="D16" s="1">
-        <v>25</v>
+      <c r="D16" s="3">
+        <v>70</v>
       </c>
       <c r="E16" s="1">
         <v>300</v>
       </c>
-      <c r="F16" s="3">
-        <v>500</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="F16" s="1">
+        <v>350</v>
+      </c>
+      <c r="G16" s="1">
         <v>2</v>
       </c>
       <c r="H16" s="1">
         <v>1.2</v>
       </c>
       <c r="I16" s="1">
-        <v>357.3</v>
+        <v>321.3</v>
       </c>
       <c r="J16" s="1">
-        <v>1837</v>
+        <v>1806</v>
       </c>
       <c r="K16" s="1">
-        <v>189.8</v>
+        <v>372.7</v>
       </c>
       <c r="L16" s="1">
-        <v>396.4</v>
+        <v>196</v>
       </c>
       <c r="M16" s="1">
-        <v>72.569999999999993</v>
+        <v>70.680000000000007</v>
       </c>
       <c r="N16" s="1">
-        <v>368.4</v>
+        <v>356.6</v>
       </c>
       <c r="O16" s="1">
-        <v>189.8</v>
-      </c>
-      <c r="P16" s="1">
-        <v>83.74</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>334.9</v>
-      </c>
-      <c r="R16" s="1">
-        <v>206.6</v>
-      </c>
-      <c r="S16" s="1">
-        <v>78.150000000000006</v>
-      </c>
-      <c r="T16" s="1"/>
+        <v>205.6</v>
+      </c>
+      <c r="P16" s="2">
+        <v>57.83</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>311.60000000000002</v>
+      </c>
+      <c r="R16" s="2">
+        <v>224.9</v>
+      </c>
+      <c r="S16" s="2">
+        <v>44.98</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -1565,46 +1593,56 @@
       <c r="C17" s="1">
         <v>2500</v>
       </c>
-      <c r="D17" s="3">
-        <v>280</v>
-      </c>
-      <c r="E17" s="1">
-        <v>300</v>
+      <c r="D17" s="1">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>100</v>
       </c>
       <c r="F17" s="1">
         <v>350</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="3">
         <v>2</v>
       </c>
       <c r="H17" s="1">
         <v>1.2</v>
       </c>
       <c r="I17" s="1">
-        <v>329.4</v>
+        <v>261</v>
       </c>
       <c r="J17" s="1">
-        <v>1898</v>
+        <v>1291</v>
       </c>
       <c r="K17" s="1">
-        <v>362.9</v>
+        <v>246.2</v>
       </c>
       <c r="L17" s="1">
-        <v>167.5</v>
+        <v>165.6</v>
       </c>
       <c r="M17" s="1">
-        <v>55.82</v>
-      </c>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
+        <v>36.81</v>
+      </c>
+      <c r="N17" s="1">
+        <v>230</v>
+      </c>
+      <c r="O17" s="1">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="P17" s="1">
+        <v>18.399999999999999</v>
+      </c>
       <c r="Q17" s="1">
-        <v>452.2</v>
-      </c>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="2" t="s">
-        <v>19</v>
+        <v>204.7</v>
+      </c>
+      <c r="R17" s="1">
+        <v>190.9</v>
+      </c>
+      <c r="S17" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
@@ -1620,52 +1658,54 @@
       <c r="D18" s="1">
         <v>25</v>
       </c>
-      <c r="E18" s="3">
-        <v>400</v>
+      <c r="E18" s="1">
+        <v>300</v>
       </c>
       <c r="F18" s="1">
         <v>350</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="1">
         <v>2</v>
       </c>
       <c r="H18" s="1">
         <v>1.2</v>
       </c>
       <c r="I18" s="1">
-        <v>328.4</v>
+        <v>312</v>
       </c>
       <c r="J18" s="1">
-        <v>1827</v>
+        <v>1635</v>
       </c>
       <c r="K18" s="1">
-        <v>332.6</v>
+        <v>308.89999999999998</v>
       </c>
       <c r="L18" s="1">
-        <v>265.3</v>
+        <v>221.1</v>
       </c>
       <c r="M18" s="1">
-        <v>50.53</v>
+        <v>66.63</v>
       </c>
       <c r="N18" s="1">
-        <v>341</v>
+        <v>284.7</v>
       </c>
       <c r="O18" s="1">
-        <v>202.1</v>
+        <v>196.9</v>
       </c>
       <c r="P18" s="1">
-        <v>63.16</v>
+        <v>60.57</v>
       </c>
       <c r="Q18" s="1">
-        <v>282.10000000000002</v>
+        <v>242.3</v>
       </c>
       <c r="R18" s="1">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="S18" s="1">
-        <v>37.89</v>
-      </c>
-      <c r="T18" s="1"/>
+        <v>27.26</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -1677,8 +1717,8 @@
       <c r="C19" s="1">
         <v>2500</v>
       </c>
-      <c r="D19" s="3">
-        <v>70</v>
+      <c r="D19" s="1">
+        <v>25</v>
       </c>
       <c r="E19" s="1">
         <v>300</v>
@@ -1686,46 +1726,48 @@
       <c r="F19" s="1">
         <v>350</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="3">
         <v>2</v>
       </c>
       <c r="H19" s="1">
         <v>1.2</v>
       </c>
       <c r="I19" s="1">
-        <v>321.3</v>
+        <v>316.8</v>
       </c>
       <c r="J19" s="1">
-        <v>1806</v>
+        <v>1836</v>
       </c>
       <c r="K19" s="1">
-        <v>372.7</v>
+        <v>307.60000000000002</v>
       </c>
       <c r="L19" s="1">
-        <v>196</v>
+        <v>193.8</v>
       </c>
       <c r="M19" s="1">
-        <v>70.680000000000007</v>
+        <v>39.99</v>
       </c>
       <c r="N19" s="1">
-        <v>356.6</v>
+        <v>301.5</v>
       </c>
       <c r="O19" s="1">
-        <v>205.6</v>
-      </c>
-      <c r="P19" s="2">
-        <v>57.83</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>311.60000000000002</v>
-      </c>
-      <c r="R19" s="2">
-        <v>224.9</v>
-      </c>
-      <c r="S19" s="2">
-        <v>44.98</v>
-      </c>
-      <c r="T19" s="1"/>
+        <v>206.1</v>
+      </c>
+      <c r="P19" s="1">
+        <v>46.14</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>295.3</v>
+      </c>
+      <c r="R19" s="1">
+        <v>279.89999999999998</v>
+      </c>
+      <c r="S19" s="1">
+        <v>30.76</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1741,51 +1783,53 @@
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F20" s="1">
         <v>350</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="1">
         <v>2</v>
       </c>
       <c r="H20" s="1">
         <v>1.2</v>
       </c>
       <c r="I20" s="1">
-        <v>261</v>
+        <v>402</v>
       </c>
       <c r="J20" s="1">
-        <v>1291</v>
+        <v>2061</v>
       </c>
       <c r="K20" s="1">
-        <v>246.2</v>
+        <v>392.3</v>
       </c>
       <c r="L20" s="1">
-        <v>165.6</v>
+        <v>244.4</v>
       </c>
       <c r="M20" s="1">
-        <v>36.81</v>
+        <v>61.1</v>
       </c>
       <c r="N20" s="1">
-        <v>230</v>
+        <v>379.4</v>
       </c>
       <c r="O20" s="1">
-        <v>147.19999999999999</v>
+        <v>238</v>
       </c>
       <c r="P20" s="1">
-        <v>18.399999999999999</v>
+        <v>57.88</v>
       </c>
       <c r="Q20" s="1">
-        <v>204.7</v>
+        <v>356.9</v>
       </c>
       <c r="R20" s="1">
-        <v>190.9</v>
+        <v>273.3</v>
       </c>
       <c r="S20" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="T20" s="1"/>
+        <v>48.23</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1807,45 +1851,47 @@
         <v>350</v>
       </c>
       <c r="G21" s="1">
-        <v>2</v>
-      </c>
-      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3">
         <v>1.2</v>
       </c>
       <c r="I21" s="1">
-        <v>312</v>
+        <v>247.3</v>
       </c>
       <c r="J21" s="1">
-        <v>1635</v>
+        <v>1156</v>
       </c>
       <c r="K21" s="1">
-        <v>308.89999999999998</v>
+        <v>249.5</v>
       </c>
       <c r="L21" s="1">
-        <v>221.1</v>
+        <v>157.6</v>
       </c>
       <c r="M21" s="1">
-        <v>66.63</v>
+        <v>32.83</v>
       </c>
       <c r="N21" s="1">
-        <v>284.7</v>
+        <v>229.8</v>
       </c>
       <c r="O21" s="1">
-        <v>196.9</v>
+        <v>177.3</v>
       </c>
       <c r="P21" s="1">
-        <v>60.57</v>
+        <v>24.07</v>
       </c>
       <c r="Q21" s="1">
-        <v>242.3</v>
+        <v>240.7</v>
       </c>
       <c r="R21" s="1">
-        <v>209</v>
+        <v>223.2</v>
       </c>
       <c r="S21" s="1">
-        <v>27.26</v>
-      </c>
-      <c r="T21" s="1"/>
+        <v>30.64</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -1863,8 +1909,8 @@
       <c r="E22" s="1">
         <v>300</v>
       </c>
-      <c r="F22" s="1">
-        <v>350</v>
+      <c r="F22" s="3">
+        <v>50</v>
       </c>
       <c r="G22" s="3">
         <v>2</v>
@@ -1873,39 +1919,41 @@
         <v>1.2</v>
       </c>
       <c r="I22" s="1">
-        <v>316.8</v>
+        <v>325.3</v>
       </c>
       <c r="J22" s="1">
-        <v>1836</v>
+        <v>1338</v>
       </c>
       <c r="K22" s="1">
-        <v>307.60000000000002</v>
+        <v>428</v>
       </c>
       <c r="L22" s="1">
-        <v>193.8</v>
+        <v>156.5</v>
       </c>
       <c r="M22" s="1">
-        <v>39.99</v>
+        <v>88.05</v>
       </c>
       <c r="N22" s="1">
-        <v>301.5</v>
+        <v>435.4</v>
       </c>
       <c r="O22" s="1">
-        <v>206.1</v>
+        <v>163.9</v>
       </c>
       <c r="P22" s="1">
-        <v>46.14</v>
+        <v>58.7</v>
       </c>
       <c r="Q22" s="1">
-        <v>295.3</v>
+        <v>366.9</v>
       </c>
       <c r="R22" s="1">
-        <v>279.89999999999998</v>
+        <v>237.3</v>
       </c>
       <c r="S22" s="1">
-        <v>30.76</v>
-      </c>
-      <c r="T22" s="1"/>
+        <v>36.69</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -1920,8 +1968,8 @@
       <c r="D23" s="1">
         <v>25</v>
       </c>
-      <c r="E23" s="3">
-        <v>600</v>
+      <c r="E23" s="1">
+        <v>300</v>
       </c>
       <c r="F23" s="1">
         <v>350</v>
@@ -1929,43 +1977,45 @@
       <c r="G23" s="1">
         <v>2</v>
       </c>
-      <c r="H23" s="1">
-        <v>1.2</v>
+      <c r="H23" s="3">
+        <v>4.8</v>
       </c>
       <c r="I23" s="1">
-        <v>402</v>
+        <v>497.7</v>
       </c>
       <c r="J23" s="1">
-        <v>2061</v>
+        <v>2480</v>
       </c>
       <c r="K23" s="1">
-        <v>392.3</v>
+        <v>545.29999999999995</v>
       </c>
       <c r="L23" s="1">
-        <v>244.4</v>
+        <v>463.1</v>
       </c>
       <c r="M23" s="1">
-        <v>61.1</v>
+        <v>125.5</v>
       </c>
       <c r="N23" s="1">
-        <v>379.4</v>
+        <v>502</v>
       </c>
       <c r="O23" s="1">
-        <v>238</v>
+        <v>389.5</v>
       </c>
       <c r="P23" s="1">
-        <v>57.88</v>
+        <v>69.239999999999995</v>
       </c>
       <c r="Q23" s="1">
-        <v>356.9</v>
+        <v>528</v>
       </c>
       <c r="R23" s="1">
-        <v>273.3</v>
+        <v>458.7</v>
       </c>
       <c r="S23" s="1">
-        <v>48.23</v>
-      </c>
-      <c r="T23" s="1"/>
+        <v>64.92</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -1986,46 +2036,48 @@
       <c r="F24" s="1">
         <v>350</v>
       </c>
-      <c r="G24" s="1">
-        <v>4</v>
+      <c r="G24" s="3">
+        <v>2</v>
       </c>
       <c r="H24" s="3">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="1">
-        <v>247.3</v>
+        <v>280.7</v>
       </c>
       <c r="J24" s="1">
-        <v>1156</v>
+        <v>2224</v>
       </c>
       <c r="K24" s="1">
-        <v>249.5</v>
+        <v>419.3</v>
       </c>
       <c r="L24" s="1">
-        <v>157.6</v>
+        <v>312.7</v>
       </c>
       <c r="M24" s="1">
-        <v>32.83</v>
+        <v>78.17</v>
       </c>
       <c r="N24" s="1">
-        <v>229.8</v>
+        <v>405.1</v>
       </c>
       <c r="O24" s="1">
-        <v>177.3</v>
+        <v>291.39999999999998</v>
       </c>
       <c r="P24" s="1">
-        <v>24.07</v>
+        <v>53.3</v>
       </c>
       <c r="Q24" s="1">
-        <v>240.7</v>
+        <v>390.8</v>
       </c>
       <c r="R24" s="1">
-        <v>223.2</v>
+        <v>309.10000000000002</v>
       </c>
       <c r="S24" s="1">
-        <v>30.64</v>
-      </c>
-      <c r="T24" s="1"/>
+        <v>39.08</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -2043,49 +2095,51 @@
       <c r="E25" s="1">
         <v>300</v>
       </c>
-      <c r="F25" s="3">
-        <v>50</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="F25" s="1">
+        <v>350</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3">
         <v>2</v>
       </c>
-      <c r="H25" s="1">
-        <v>1.2</v>
-      </c>
       <c r="I25" s="1">
-        <v>325.3</v>
+        <v>466.7</v>
       </c>
       <c r="J25" s="1">
-        <v>1338</v>
+        <v>2725</v>
       </c>
       <c r="K25" s="1">
-        <v>428</v>
+        <v>466.7</v>
       </c>
       <c r="L25" s="1">
-        <v>156.5</v>
+        <v>264</v>
       </c>
       <c r="M25" s="1">
-        <v>88.05</v>
+        <v>51.85</v>
       </c>
       <c r="N25" s="1">
-        <v>435.4</v>
+        <v>447.8</v>
       </c>
       <c r="O25" s="1">
-        <v>163.9</v>
+        <v>231</v>
       </c>
       <c r="P25" s="1">
-        <v>58.7</v>
+        <v>51.85</v>
       </c>
       <c r="Q25" s="1">
-        <v>366.9</v>
+        <v>471.4</v>
       </c>
       <c r="R25" s="1">
-        <v>237.3</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="S25" s="1">
-        <v>36.69</v>
-      </c>
-      <c r="T25" s="1"/>
+        <v>28.28</v>
+      </c>
+      <c r="T25" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -2107,45 +2161,47 @@
         <v>350</v>
       </c>
       <c r="G26" s="1">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H26" s="3">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I26" s="1">
-        <v>497.7</v>
+        <v>474</v>
       </c>
       <c r="J26" s="1">
-        <v>2480</v>
+        <v>1746</v>
       </c>
       <c r="K26" s="1">
-        <v>545.29999999999995</v>
+        <v>366.2</v>
       </c>
       <c r="L26" s="1">
-        <v>463.1</v>
+        <v>258.3</v>
       </c>
       <c r="M26" s="1">
-        <v>125.5</v>
+        <v>70.97</v>
       </c>
       <c r="N26" s="1">
-        <v>502</v>
+        <v>337.8</v>
       </c>
       <c r="O26" s="1">
-        <v>389.5</v>
+        <v>232.8</v>
       </c>
       <c r="P26" s="1">
-        <v>69.239999999999995</v>
+        <v>48.26</v>
       </c>
       <c r="Q26" s="1">
-        <v>528</v>
+        <v>315.10000000000002</v>
       </c>
       <c r="R26" s="1">
-        <v>458.7</v>
+        <v>249.8</v>
       </c>
       <c r="S26" s="1">
-        <v>64.92</v>
-      </c>
-      <c r="T26" s="1"/>
+        <v>39.74</v>
+      </c>
+      <c r="T26" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -2166,46 +2222,48 @@
       <c r="F27" s="1">
         <v>350</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="1">
         <v>2</v>
       </c>
       <c r="H27" s="3">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="I27" s="1">
-        <v>280.7</v>
+        <v>410.3</v>
       </c>
       <c r="J27" s="1">
-        <v>2224</v>
+        <v>2055</v>
       </c>
       <c r="K27" s="1">
-        <v>419.3</v>
+        <v>369.2</v>
       </c>
       <c r="L27" s="1">
-        <v>312.7</v>
+        <v>218.8</v>
       </c>
       <c r="M27" s="1">
-        <v>78.17</v>
+        <v>41.03</v>
       </c>
       <c r="N27" s="1">
-        <v>405.1</v>
+        <v>365.8</v>
       </c>
       <c r="O27" s="1">
-        <v>291.39999999999998</v>
+        <v>218.8</v>
       </c>
       <c r="P27" s="1">
-        <v>53.3</v>
+        <v>30.77</v>
       </c>
       <c r="Q27" s="1">
-        <v>390.8</v>
+        <v>376.1</v>
       </c>
       <c r="R27" s="1">
-        <v>309.10000000000002</v>
+        <v>314.5</v>
       </c>
       <c r="S27" s="1">
-        <v>39.08</v>
-      </c>
-      <c r="T27" s="1"/>
+        <v>23.93</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -2227,285 +2285,298 @@
         <v>350</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="3">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I28" s="1">
-        <v>466.7</v>
+        <v>413.1</v>
       </c>
       <c r="J28" s="1">
-        <v>2725</v>
+        <v>2059</v>
       </c>
       <c r="K28" s="1">
-        <v>466.7</v>
+        <v>402.7</v>
       </c>
       <c r="L28" s="1">
-        <v>264</v>
+        <v>211.8</v>
       </c>
       <c r="M28" s="1">
-        <v>51.85</v>
+        <v>48.6</v>
       </c>
       <c r="N28" s="1">
-        <v>447.8</v>
+        <v>388.8</v>
       </c>
       <c r="O28" s="1">
-        <v>231</v>
+        <v>232.6</v>
       </c>
       <c r="P28" s="1">
-        <v>51.85</v>
+        <v>41.66</v>
       </c>
       <c r="Q28" s="1">
-        <v>471.4</v>
+        <v>399.2</v>
       </c>
       <c r="R28" s="1">
-        <v>306.39999999999998</v>
+        <v>302</v>
       </c>
       <c r="S28" s="1">
-        <v>28.28</v>
-      </c>
-      <c r="T28" s="1"/>
+        <v>31.24</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B29" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C29" s="1">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="D29" s="1">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E29" s="1">
-        <v>300</v>
-      </c>
-      <c r="F29" s="1">
-        <v>350</v>
+        <v>500</v>
+      </c>
+      <c r="F29" s="3">
+        <v>500</v>
       </c>
       <c r="G29" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="H29" s="1">
         <v>2.4</v>
       </c>
-      <c r="H29" s="3">
-        <v>2.4</v>
-      </c>
       <c r="I29" s="1">
-        <v>474</v>
+        <v>308.2</v>
       </c>
       <c r="J29" s="1">
-        <v>1746</v>
+        <v>3123</v>
       </c>
       <c r="K29" s="1">
-        <v>366.2</v>
+        <v>462.3</v>
       </c>
       <c r="L29" s="1">
-        <v>258.3</v>
+        <v>364.7</v>
       </c>
       <c r="M29" s="1">
-        <v>70.97</v>
+        <v>77.05</v>
       </c>
       <c r="N29" s="1">
-        <v>337.8</v>
+        <v>431.5</v>
       </c>
       <c r="O29" s="1">
-        <v>232.8</v>
+        <v>313.39999999999998</v>
       </c>
       <c r="P29" s="1">
-        <v>48.26</v>
+        <v>61.64</v>
       </c>
       <c r="Q29" s="1">
-        <v>315.10000000000002</v>
+        <v>421.2</v>
       </c>
       <c r="R29" s="1">
-        <v>249.8</v>
+        <v>303.10000000000002</v>
       </c>
       <c r="S29" s="1">
-        <v>39.74</v>
-      </c>
-      <c r="T29" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="T29" s="1">
+        <v>0</v>
+      </c>
+      <c r="U29" s="1"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B30" s="1">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C30" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D30" s="1">
-        <v>25</v>
-      </c>
-      <c r="E30" s="1">
-        <v>300</v>
-      </c>
-      <c r="F30" s="1">
-        <v>350</v>
+        <v>100</v>
+      </c>
+      <c r="E30" s="3">
+        <v>500</v>
+      </c>
+      <c r="F30" s="3">
+        <v>450</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
       </c>
-      <c r="H30" s="3">
-        <v>1.2</v>
+      <c r="H30" s="1">
+        <v>1.6</v>
       </c>
       <c r="I30" s="1">
-        <v>410.3</v>
+        <v>485.4</v>
       </c>
       <c r="J30" s="1">
-        <v>2055</v>
+        <v>2494</v>
       </c>
       <c r="K30" s="1">
-        <v>369.2</v>
+        <v>434.1</v>
       </c>
       <c r="L30" s="1">
-        <v>218.8</v>
+        <v>284.10000000000002</v>
       </c>
       <c r="M30" s="1">
-        <v>41.03</v>
+        <v>71.03</v>
       </c>
       <c r="N30" s="1">
-        <v>365.8</v>
+        <v>410.4</v>
       </c>
       <c r="O30" s="1">
-        <v>218.8</v>
+        <v>256.5</v>
       </c>
       <c r="P30" s="1">
-        <v>30.77</v>
+        <v>47.36</v>
       </c>
       <c r="Q30" s="1">
-        <v>376.1</v>
+        <v>418.3</v>
       </c>
       <c r="R30" s="1">
-        <v>314.5</v>
+        <v>276.2</v>
       </c>
       <c r="S30" s="1">
-        <v>23.93</v>
-      </c>
-      <c r="T30" s="1"/>
+        <v>39.46</v>
+      </c>
+      <c r="T30" s="1">
+        <v>0</v>
+      </c>
+      <c r="U30" s="1"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C31" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D31" s="1">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1">
-        <v>300</v>
-      </c>
-      <c r="F31" s="1">
-        <v>350</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2</v>
-      </c>
-      <c r="H31" s="3">
-        <v>1.2</v>
+        <v>250</v>
+      </c>
+      <c r="F31" s="3">
+        <v>100</v>
+      </c>
+      <c r="G31" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1.6</v>
       </c>
       <c r="I31" s="1">
-        <v>413.1</v>
+        <v>298.3</v>
       </c>
       <c r="J31" s="1">
-        <v>2059</v>
+        <v>2217</v>
       </c>
       <c r="K31" s="1">
-        <v>402.7</v>
+        <v>449.3</v>
       </c>
       <c r="L31" s="1">
-        <v>211.8</v>
+        <v>235.7</v>
       </c>
       <c r="M31" s="1">
-        <v>48.6</v>
+        <v>47.88</v>
       </c>
       <c r="N31" s="1">
-        <v>388.8</v>
+        <v>445.7</v>
       </c>
       <c r="O31" s="1">
-        <v>232.6</v>
+        <v>202.6</v>
       </c>
       <c r="P31" s="1">
-        <v>41.66</v>
+        <v>29.46</v>
       </c>
       <c r="Q31" s="1">
-        <v>399.2</v>
+        <v>427.2</v>
       </c>
       <c r="R31" s="1">
-        <v>302</v>
+        <v>265.2</v>
       </c>
       <c r="S31" s="1">
-        <v>31.24</v>
-      </c>
-      <c r="T31" s="1"/>
+        <v>18.420000000000002</v>
+      </c>
+      <c r="T31" s="1">
+        <v>0</v>
+      </c>
+      <c r="U31" s="1"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C32" s="1">
-        <v>2100</v>
+        <v>2900</v>
       </c>
       <c r="D32" s="1">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="E32" s="1">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
-        <v>500</v>
-      </c>
-      <c r="G32" s="1">
-        <v>3.2</v>
+      <c r="F32" s="1">
+        <v>200</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2</v>
       </c>
       <c r="H32" s="1">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="I32" s="1">
-        <v>308.2</v>
+        <v>526.5</v>
       </c>
       <c r="J32" s="1">
-        <v>3123</v>
+        <v>2211</v>
       </c>
       <c r="K32" s="1">
-        <v>462.3</v>
+        <v>503.9</v>
       </c>
       <c r="L32" s="1">
-        <v>364.7</v>
+        <v>270.8</v>
       </c>
       <c r="M32" s="1">
-        <v>77.05</v>
+        <v>67.69</v>
       </c>
       <c r="N32" s="1">
-        <v>431.5</v>
+        <v>488.9</v>
       </c>
       <c r="O32" s="1">
-        <v>313.39999999999998</v>
+        <v>229.4</v>
       </c>
       <c r="P32" s="1">
-        <v>61.64</v>
+        <v>48.89</v>
       </c>
       <c r="Q32" s="1">
-        <v>421.2</v>
+        <v>473.8</v>
       </c>
       <c r="R32" s="1">
-        <v>303.10000000000002</v>
+        <v>282</v>
       </c>
       <c r="S32" s="1">
-        <v>10</v>
-      </c>
-      <c r="T32" s="1"/>
+        <v>30.08</v>
+      </c>
+      <c r="T32" s="1">
+        <v>0</v>
+      </c>
       <c r="U32" s="1"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.3">
@@ -2513,192 +2584,196 @@
         <v>51</v>
       </c>
       <c r="B33" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C33" s="1">
-        <v>2900</v>
-      </c>
-      <c r="D33" s="3">
-        <v>95</v>
+        <v>2400</v>
+      </c>
+      <c r="D33" s="1">
+        <v>35</v>
       </c>
       <c r="E33" s="1">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="F33" s="1">
-        <v>100</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2.2000000000000002</v>
+        <v>400</v>
+      </c>
+      <c r="G33" s="3">
+        <v>2.4</v>
       </c>
       <c r="H33" s="1">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="I33" s="1">
-        <v>351.2</v>
+        <v>393.7</v>
       </c>
       <c r="J33" s="1">
-        <v>1492</v>
+        <v>2278</v>
       </c>
       <c r="K33" s="1">
-        <v>430.5</v>
+        <v>368.1</v>
       </c>
       <c r="L33" s="1">
-        <v>165</v>
+        <v>262.39999999999998</v>
       </c>
       <c r="M33" s="1">
-        <v>0</v>
+        <v>61.96</v>
       </c>
       <c r="N33" s="1">
-        <v>480.6</v>
+        <v>346.3</v>
       </c>
       <c r="O33" s="1">
-        <v>165</v>
+        <v>240.6</v>
       </c>
       <c r="P33" s="1">
-        <v>0</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="Q33" s="1">
-        <v>475.4</v>
+        <v>320.8</v>
       </c>
       <c r="R33" s="1">
-        <v>165</v>
+        <v>251.5</v>
       </c>
       <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>52</v>
+        <v>25.51</v>
+      </c>
+      <c r="T33" s="1">
+        <v>0</v>
       </c>
       <c r="U33" s="1"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B34" s="1">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="D34" s="1">
-        <v>100</v>
-      </c>
-      <c r="E34" s="3">
-        <v>500</v>
-      </c>
-      <c r="F34" s="3">
-        <v>450</v>
-      </c>
-      <c r="G34" s="1">
+        <v>25</v>
+      </c>
+      <c r="E34" s="1">
+        <v>50</v>
+      </c>
+      <c r="F34" s="1">
+        <v>200</v>
+      </c>
+      <c r="G34" s="3">
         <v>2</v>
       </c>
       <c r="H34" s="1">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="I34" s="1">
-        <v>485.4</v>
+        <v>334</v>
       </c>
       <c r="J34" s="1">
-        <v>2494</v>
+        <v>1587</v>
       </c>
       <c r="K34" s="1">
-        <v>434.1</v>
+        <v>354.1</v>
       </c>
       <c r="L34" s="1">
-        <v>284.10000000000002</v>
+        <v>168.3</v>
       </c>
       <c r="M34" s="1">
-        <v>71.03</v>
+        <v>20.09</v>
       </c>
       <c r="N34" s="1">
-        <v>410.4</v>
+        <v>349.1</v>
       </c>
       <c r="O34" s="1">
-        <v>256.5</v>
+        <v>168.3</v>
       </c>
       <c r="P34" s="1">
-        <v>47.36</v>
+        <v>12.56</v>
       </c>
       <c r="Q34" s="1">
-        <v>418.3</v>
+        <v>354.1</v>
       </c>
       <c r="R34" s="1">
-        <v>276.2</v>
+        <v>168.3</v>
       </c>
       <c r="S34" s="1">
-        <v>39.46</v>
-      </c>
-      <c r="T34" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="T34" s="1">
+        <v>0</v>
+      </c>
       <c r="U34" s="1"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C35" s="1">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="D35" s="1">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E35" s="1">
-        <v>250</v>
-      </c>
-      <c r="F35" s="3">
-        <v>100</v>
+        <v>200</v>
+      </c>
+      <c r="F35" s="1">
+        <v>450</v>
       </c>
       <c r="G35" s="3">
         <v>2.4</v>
       </c>
       <c r="H35" s="1">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>298.3</v>
+        <v>338.9</v>
       </c>
       <c r="J35" s="1">
-        <v>2217</v>
+        <v>2057</v>
       </c>
       <c r="K35" s="1">
-        <v>449.3</v>
+        <v>328.7</v>
       </c>
       <c r="L35" s="1">
-        <v>235.7</v>
+        <v>267.7</v>
       </c>
       <c r="M35" s="1">
-        <v>47.88</v>
+        <v>61</v>
       </c>
       <c r="N35" s="1">
-        <v>445.7</v>
+        <v>349.1</v>
       </c>
       <c r="O35" s="1">
-        <v>202.6</v>
+        <v>233.8</v>
       </c>
       <c r="P35" s="1">
-        <v>29.46</v>
+        <v>64.39</v>
       </c>
       <c r="Q35" s="1">
-        <v>427.2</v>
+        <v>284.7</v>
       </c>
       <c r="R35" s="1">
-        <v>265.2</v>
+        <v>233.8</v>
       </c>
       <c r="S35" s="1">
-        <v>18.420000000000002</v>
-      </c>
-      <c r="T35" s="1"/>
+        <v>40.67</v>
+      </c>
+      <c r="T35" s="1">
+        <v>0</v>
+      </c>
       <c r="U35" s="1"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C36" s="1">
         <v>2900</v>
@@ -2707,727 +2782,707 @@
         <v>25</v>
       </c>
       <c r="E36" s="1">
+        <v>200</v>
+      </c>
+      <c r="F36" s="3">
         <v>500</v>
       </c>
-      <c r="F36" s="1">
-        <v>200</v>
-      </c>
-      <c r="G36" s="3">
+      <c r="G36" s="1">
         <v>2</v>
       </c>
       <c r="H36" s="1">
         <v>1.2</v>
       </c>
       <c r="I36" s="1">
-        <v>526.5</v>
+        <v>221</v>
       </c>
       <c r="J36" s="1">
-        <v>2211</v>
+        <v>1402</v>
       </c>
       <c r="K36" s="1">
-        <v>503.9</v>
+        <v>292.3</v>
       </c>
       <c r="L36" s="1">
-        <v>270.8</v>
+        <v>178.3</v>
       </c>
       <c r="M36" s="1">
-        <v>67.69</v>
+        <v>42.78</v>
       </c>
       <c r="N36" s="1">
-        <v>488.9</v>
+        <v>266.2</v>
       </c>
       <c r="O36" s="1">
-        <v>229.4</v>
+        <v>171.1</v>
       </c>
       <c r="P36" s="1">
-        <v>48.89</v>
+        <v>38.03</v>
       </c>
       <c r="Q36" s="1">
-        <v>473.8</v>
+        <v>244.8</v>
       </c>
       <c r="R36" s="1">
-        <v>282</v>
+        <v>185.4</v>
       </c>
       <c r="S36" s="1">
-        <v>30.08</v>
-      </c>
-      <c r="T36" s="1"/>
+        <v>23.77</v>
+      </c>
+      <c r="T36" s="1">
+        <v>0</v>
+      </c>
       <c r="U36" s="1"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="1">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D37" s="1">
+        <v>95</v>
+      </c>
+      <c r="E37" s="1">
+        <v>400</v>
+      </c>
+      <c r="F37" s="1">
+        <v>100</v>
+      </c>
+      <c r="G37" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I37" s="1">
+        <v>375.5</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2030</v>
+      </c>
+      <c r="K37" s="1">
+        <v>400</v>
+      </c>
+      <c r="L37" s="1">
+        <v>225</v>
+      </c>
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1">
+        <v>534.6</v>
+      </c>
+      <c r="O37" s="1">
+        <v>225</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>578.5</v>
+      </c>
+      <c r="R37" s="1">
+        <v>225</v>
+      </c>
+      <c r="S37" s="1">
+        <v>1</v>
+      </c>
+      <c r="T37" s="1">
+        <v>0</v>
+      </c>
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="1">
-        <v>15</v>
-      </c>
-      <c r="C37" s="1">
-        <v>2400</v>
-      </c>
-      <c r="D37" s="1">
-        <v>35</v>
-      </c>
-      <c r="E37" s="1">
-        <v>350</v>
-      </c>
-      <c r="F37" s="1">
-        <v>400</v>
-      </c>
-      <c r="G37" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="H37" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="I37" s="1">
-        <v>393.7</v>
-      </c>
-      <c r="J37" s="1">
-        <v>2278</v>
-      </c>
-      <c r="K37" s="1">
-        <v>368.1</v>
-      </c>
-      <c r="L37" s="1">
-        <v>262.39999999999998</v>
-      </c>
-      <c r="M37" s="1">
-        <v>61.96</v>
-      </c>
-      <c r="N37" s="1">
-        <v>346.3</v>
-      </c>
-      <c r="O37" s="1">
-        <v>240.6</v>
-      </c>
-      <c r="P37" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>320.8</v>
-      </c>
-      <c r="R37" s="1">
-        <v>251.5</v>
-      </c>
-      <c r="S37" s="1">
-        <v>25.51</v>
-      </c>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-    </row>
-    <row r="38" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="5">
+      <c r="B38" s="1">
         <v>30</v>
       </c>
-      <c r="C38" s="5">
-        <v>2700</v>
-      </c>
-      <c r="D38" s="5">
-        <v>25</v>
-      </c>
-      <c r="E38" s="5">
-        <v>50</v>
-      </c>
-      <c r="F38" s="5">
-        <v>200</v>
-      </c>
-      <c r="G38" s="6">
+      <c r="C38" s="1">
+        <v>2800</v>
+      </c>
+      <c r="D38" s="1">
+        <v>75</v>
+      </c>
+      <c r="E38" s="3">
+        <v>500</v>
+      </c>
+      <c r="F38" s="3">
+        <v>300</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="H38" s="1">
         <v>2</v>
       </c>
-      <c r="H38" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="I38" s="5">
-        <v>334</v>
-      </c>
-      <c r="J38" s="5">
-        <v>1587</v>
-      </c>
-      <c r="K38" s="5">
-        <v>354.1</v>
-      </c>
-      <c r="L38" s="5">
-        <v>168.3</v>
-      </c>
-      <c r="M38" s="5">
-        <v>20.09</v>
-      </c>
-      <c r="N38" s="5">
-        <v>349.1</v>
-      </c>
-      <c r="O38" s="5">
-        <v>168.3</v>
-      </c>
-      <c r="P38" s="5">
-        <v>12.56</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>354.1</v>
-      </c>
-      <c r="R38" s="5">
-        <v>168.3</v>
-      </c>
-      <c r="S38" s="5">
-        <v>0</v>
-      </c>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
+      <c r="I38" s="1">
+        <v>361.9</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2659</v>
+      </c>
+      <c r="K38" s="1">
+        <v>440.6</v>
+      </c>
+      <c r="L38" s="1">
+        <v>304.2</v>
+      </c>
+      <c r="M38" s="1">
+        <v>78.67</v>
+      </c>
+      <c r="N38" s="1">
+        <v>430.1</v>
+      </c>
+      <c r="O38" s="1">
+        <v>272.7</v>
+      </c>
+      <c r="P38" s="1">
+        <v>47.2</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>430.1</v>
+      </c>
+      <c r="R38" s="1">
+        <v>262.2</v>
+      </c>
+      <c r="S38" s="1">
+        <v>20.98</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="1">
+        <v>15</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D39" s="1">
+        <v>25</v>
+      </c>
+      <c r="E39" s="1">
         <v>50</v>
       </c>
-      <c r="C39" s="1">
-        <v>2400</v>
-      </c>
-      <c r="D39" s="1">
-        <v>25</v>
-      </c>
-      <c r="E39" s="1">
-        <v>200</v>
-      </c>
       <c r="F39" s="1">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="G39" s="3">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="H39" s="1">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I39" s="1">
-        <v>338.9</v>
+        <v>321.89999999999998</v>
       </c>
       <c r="J39" s="1">
-        <v>2057</v>
+        <v>1000.9</v>
       </c>
       <c r="K39" s="1">
-        <v>328.7</v>
+        <v>314.5</v>
       </c>
       <c r="L39" s="1">
-        <v>267.7</v>
+        <v>107.9</v>
       </c>
       <c r="M39" s="1">
-        <v>61</v>
+        <v>14.89</v>
       </c>
       <c r="N39" s="1">
-        <v>349.1</v>
+        <v>316.3</v>
       </c>
       <c r="O39" s="1">
-        <v>233.8</v>
+        <v>104.2</v>
       </c>
       <c r="P39" s="1">
-        <v>64.39</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="Q39" s="1">
-        <v>284.7</v>
+        <v>323.8</v>
       </c>
       <c r="R39" s="1">
-        <v>233.8</v>
+        <v>189.8</v>
       </c>
       <c r="S39" s="1">
-        <v>40.67</v>
-      </c>
-      <c r="T39" s="1"/>
+        <v>7.44</v>
+      </c>
+      <c r="T39" s="1">
+        <v>0</v>
+      </c>
       <c r="U39" s="1"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="1">
+        <v>30</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2200</v>
+      </c>
+      <c r="D40" s="1">
+        <v>90</v>
+      </c>
+      <c r="E40" s="1">
+        <v>500</v>
+      </c>
+      <c r="F40" s="3">
+        <v>100</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I40" s="1">
+        <v>424</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1502</v>
+      </c>
+      <c r="K40" s="1">
+        <v>515.79999999999995</v>
+      </c>
+      <c r="L40" s="1">
+        <v>150</v>
+      </c>
+      <c r="M40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1">
+        <v>568.79999999999995</v>
+      </c>
+      <c r="O40" s="1">
+        <v>150</v>
+      </c>
+      <c r="P40" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>568.79999999999995</v>
+      </c>
+      <c r="R40" s="1">
+        <v>150</v>
+      </c>
+      <c r="S40" s="1">
+        <v>1</v>
+      </c>
+      <c r="T40" s="1">
+        <v>1</v>
+      </c>
+      <c r="U40" s="1"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B41" s="1">
         <v>50</v>
       </c>
-      <c r="C40" s="1">
-        <v>2900</v>
-      </c>
-      <c r="D40" s="1">
-        <v>25</v>
-      </c>
-      <c r="E40" s="1">
-        <v>200</v>
-      </c>
-      <c r="F40" s="3">
+      <c r="C41" s="1">
+        <v>2300</v>
+      </c>
+      <c r="D41" s="1">
+        <v>25</v>
+      </c>
+      <c r="E41" s="1">
+        <v>350</v>
+      </c>
+      <c r="F41" s="1">
         <v>500</v>
       </c>
-      <c r="G40" s="1">
-        <v>2</v>
-      </c>
-      <c r="H40" s="1">
+      <c r="G41" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="H41" s="1">
         <v>1.2</v>
       </c>
-      <c r="I40" s="1">
-        <v>221</v>
-      </c>
-      <c r="J40" s="1">
-        <v>1402</v>
-      </c>
-      <c r="K40" s="1">
-        <v>292.3</v>
-      </c>
-      <c r="L40" s="1">
-        <v>178.3</v>
-      </c>
-      <c r="M40" s="1">
-        <v>42.78</v>
-      </c>
-      <c r="N40" s="1">
-        <v>266.2</v>
-      </c>
-      <c r="O40" s="1">
-        <v>171.1</v>
-      </c>
-      <c r="P40" s="1">
-        <v>38.03</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>244.8</v>
-      </c>
-      <c r="R40" s="1">
-        <v>185.4</v>
-      </c>
-      <c r="S40" s="1">
-        <v>23.77</v>
-      </c>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-    </row>
-    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="5">
-        <v>20</v>
-      </c>
-      <c r="C41" s="5">
-        <v>3000</v>
-      </c>
-      <c r="D41" s="5">
-        <v>95</v>
-      </c>
-      <c r="E41" s="5">
-        <v>400</v>
-      </c>
-      <c r="F41" s="5">
-        <v>100</v>
-      </c>
-      <c r="G41" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="H41" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="I41" s="5">
-        <v>375.5</v>
-      </c>
-      <c r="J41" s="5">
-        <v>2030</v>
-      </c>
-      <c r="K41" s="5">
-        <v>400</v>
-      </c>
-      <c r="L41" s="5">
-        <v>225</v>
-      </c>
-      <c r="M41" s="5">
-        <v>0</v>
-      </c>
-      <c r="N41" s="5">
-        <v>534.6</v>
-      </c>
-      <c r="O41" s="5">
-        <v>225</v>
-      </c>
-      <c r="P41" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="5">
-        <v>578.5</v>
-      </c>
-      <c r="R41" s="5">
-        <v>225</v>
-      </c>
-      <c r="S41" s="5">
-        <v>0</v>
-      </c>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
+      <c r="I41" s="1">
+        <v>348.9</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1630</v>
+      </c>
+      <c r="K41" s="1">
+        <v>332.2</v>
+      </c>
+      <c r="L41" s="1">
+        <v>198.2</v>
+      </c>
+      <c r="M41" s="1">
+        <v>72.569999999999993</v>
+      </c>
+      <c r="N41" s="1">
+        <v>295.89999999999998</v>
+      </c>
+      <c r="O41" s="1">
+        <v>173.1</v>
+      </c>
+      <c r="P41" s="1">
+        <v>44.66</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>256.8</v>
+      </c>
+      <c r="R41" s="1">
+        <v>187</v>
+      </c>
+      <c r="S41" s="1">
+        <v>30.7</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="1">
+        <v>35</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2700</v>
+      </c>
+      <c r="D42" s="1">
+        <v>25</v>
+      </c>
+      <c r="E42" s="1">
+        <v>300</v>
+      </c>
+      <c r="F42" s="1">
+        <v>500</v>
+      </c>
+      <c r="G42" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="I42" s="1">
+        <v>233.4</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1962</v>
+      </c>
+      <c r="K42" s="1">
+        <v>301.10000000000002</v>
+      </c>
+      <c r="L42" s="1">
+        <v>270.7</v>
+      </c>
+      <c r="M42" s="1">
+        <v>67.67</v>
+      </c>
+      <c r="N42" s="1">
+        <v>294.3</v>
+      </c>
+      <c r="O42" s="1">
+        <v>236.8</v>
+      </c>
+      <c r="P42" s="1">
+        <v>57.52</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>216.5</v>
+      </c>
+      <c r="R42" s="1">
+        <v>196.2</v>
+      </c>
+      <c r="S42" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="1">
-        <v>30</v>
-      </c>
-      <c r="C42" s="1">
-        <v>2800</v>
-      </c>
-      <c r="D42" s="1">
-        <v>75</v>
-      </c>
-      <c r="E42" s="3">
-        <v>500</v>
-      </c>
-      <c r="F42" s="3">
-        <v>300</v>
-      </c>
-      <c r="G42" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="H42" s="1">
-        <v>2</v>
-      </c>
-      <c r="I42" s="1">
-        <v>361.9</v>
-      </c>
-      <c r="J42" s="1">
-        <v>2659</v>
-      </c>
-      <c r="K42" s="1">
-        <v>440.6</v>
-      </c>
-      <c r="L42" s="1">
-        <v>304.2</v>
-      </c>
-      <c r="M42" s="1">
-        <v>78.67</v>
-      </c>
-      <c r="N42" s="1">
-        <v>430.1</v>
-      </c>
-      <c r="O42" s="1">
-        <v>272.7</v>
-      </c>
-      <c r="P42" s="1">
-        <v>47.2</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>430.1</v>
-      </c>
-      <c r="R42" s="1">
-        <v>262.2</v>
-      </c>
-      <c r="S42" s="1">
-        <v>20.98</v>
-      </c>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-    </row>
-    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="5">
-        <v>15</v>
-      </c>
-      <c r="C43" s="5">
-        <v>2900</v>
-      </c>
-      <c r="D43" s="5">
-        <v>25</v>
-      </c>
-      <c r="E43" s="5">
-        <v>50</v>
-      </c>
-      <c r="F43" s="5">
-        <v>150</v>
-      </c>
-      <c r="G43" s="6">
-        <v>2</v>
-      </c>
-      <c r="H43" s="5">
+      <c r="B43" s="1">
+        <v>25</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D43" s="1">
+        <v>25</v>
+      </c>
+      <c r="E43" s="1">
+        <v>250</v>
+      </c>
+      <c r="F43" s="1">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
         <v>1.2</v>
       </c>
-      <c r="I43" s="5">
-        <v>321.89999999999998</v>
-      </c>
-      <c r="J43" s="5">
-        <v>1000.9</v>
-      </c>
-      <c r="K43" s="5">
-        <v>314.5</v>
-      </c>
-      <c r="L43" s="5">
-        <v>107.9</v>
-      </c>
-      <c r="M43" s="5">
-        <v>14.89</v>
-      </c>
-      <c r="N43" s="5">
-        <v>316.3</v>
-      </c>
-      <c r="O43" s="5">
-        <v>104.2</v>
-      </c>
-      <c r="P43" s="5">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="Q43" s="5">
-        <v>323.8</v>
-      </c>
-      <c r="R43" s="5">
-        <v>189.8</v>
-      </c>
-      <c r="S43" s="5">
-        <v>7.44</v>
-      </c>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
+      <c r="H43" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I43" s="1">
+        <v>435.4</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1368</v>
+      </c>
+      <c r="K43" s="1">
+        <v>450</v>
+      </c>
+      <c r="L43" s="1">
+        <v>136</v>
+      </c>
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1">
+        <v>488.5</v>
+      </c>
+      <c r="O43" s="1">
+        <v>136</v>
+      </c>
+      <c r="P43" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>522</v>
+      </c>
+      <c r="R43" s="1">
+        <v>136</v>
+      </c>
+      <c r="S43" s="1">
+        <v>1</v>
+      </c>
+      <c r="T43" s="1">
+        <v>1</v>
+      </c>
+      <c r="U43" s="1"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C44" s="1">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="D44" s="1">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="E44" s="1">
-        <v>500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>100</v>
+        <v>300</v>
+      </c>
+      <c r="F44" s="1">
+        <v>450</v>
       </c>
       <c r="G44" s="3">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H44" s="1">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I44" s="1">
-        <v>424</v>
+        <v>374.1</v>
       </c>
       <c r="J44" s="1">
-        <v>1502</v>
+        <v>1477</v>
       </c>
       <c r="K44" s="1">
-        <v>515.79999999999995</v>
+        <v>357.2</v>
       </c>
       <c r="L44" s="1">
-        <v>150</v>
+        <v>197.9</v>
       </c>
       <c r="M44" s="1">
-        <v>0</v>
+        <v>50.68</v>
       </c>
       <c r="N44" s="1">
-        <v>568.79999999999995</v>
+        <v>316.2</v>
       </c>
       <c r="O44" s="1">
-        <v>150</v>
+        <v>166.5</v>
       </c>
       <c r="P44" s="1">
-        <v>0</v>
+        <v>50.68</v>
       </c>
       <c r="Q44" s="1">
-        <v>568.79999999999995</v>
+        <v>260.7</v>
       </c>
       <c r="R44" s="1">
-        <v>150</v>
+        <v>166.5</v>
       </c>
       <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>28.96</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C45" s="1">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="D45" s="1">
-        <v>25</v>
-      </c>
-      <c r="E45" s="1">
-        <v>350</v>
-      </c>
-      <c r="F45" s="1">
-        <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2.4</v>
+        <v>30</v>
+      </c>
+      <c r="E45" s="3">
+        <v>250</v>
+      </c>
+      <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
       </c>
       <c r="H45" s="1">
         <v>1.2</v>
       </c>
       <c r="I45" s="1">
-        <v>348.9</v>
+        <v>306</v>
       </c>
       <c r="J45" s="1">
-        <v>1630</v>
+        <v>1363</v>
       </c>
       <c r="K45" s="1">
-        <v>332.2</v>
+        <v>332.3</v>
       </c>
       <c r="L45" s="1">
-        <v>198.2</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="M45" s="1">
-        <v>72.569999999999993</v>
+        <v>62.16</v>
       </c>
       <c r="N45" s="1">
-        <v>295.89999999999998</v>
+        <v>306</v>
       </c>
       <c r="O45" s="1">
-        <v>173.1</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="P45" s="1">
-        <v>44.66</v>
+        <v>50.21</v>
       </c>
       <c r="Q45" s="1">
-        <v>256.8</v>
+        <v>267.8</v>
       </c>
       <c r="R45" s="1">
-        <v>187</v>
+        <v>169.8</v>
       </c>
       <c r="S45" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
+        <v>31.08</v>
+      </c>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="1">
-        <v>35</v>
-      </c>
-      <c r="C46" s="1">
-        <v>2700</v>
-      </c>
-      <c r="D46" s="1">
-        <v>25</v>
-      </c>
-      <c r="E46" s="1">
-        <v>300</v>
-      </c>
-      <c r="F46" s="1">
-        <v>500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="H46" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="I46" s="1">
-        <v>233.4</v>
-      </c>
-      <c r="J46" s="1">
-        <v>1962</v>
-      </c>
-      <c r="K46" s="1">
-        <v>301.10000000000002</v>
-      </c>
-      <c r="L46" s="1">
-        <v>270.7</v>
-      </c>
-      <c r="M46" s="1">
-        <v>67.67</v>
-      </c>
-      <c r="N46" s="1">
-        <v>294.3</v>
-      </c>
-      <c r="O46" s="1">
-        <v>236.8</v>
-      </c>
-      <c r="P46" s="1">
-        <v>57.52</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>216.5</v>
-      </c>
-      <c r="R46" s="1">
-        <v>196.2</v>
-      </c>
-      <c r="S46" s="1">
-        <v>40.6</v>
-      </c>
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
       <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="1">
-        <v>25</v>
-      </c>
-      <c r="C47" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D47" s="1">
-        <v>25</v>
-      </c>
-      <c r="E47" s="1">
-        <v>250</v>
-      </c>
-      <c r="F47" s="1">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="I47" s="1">
-        <v>435.4</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1368</v>
-      </c>
-      <c r="K47" s="1">
-        <v>450</v>
-      </c>
-      <c r="L47" s="1">
-        <v>136</v>
-      </c>
-      <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <v>488.5</v>
-      </c>
-      <c r="O47" s="1">
-        <v>136</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>522</v>
-      </c>
-      <c r="R47" s="1">
-        <v>136</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="U47" s="1"/>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
